--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260624.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>14.51%</t>
+          <t>14.43%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>13.45%</t>
+          <t>13.25%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>11.63%</t>
+          <t>11.81%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>11.46%</t>
+          <t>11.25%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>4.25%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.83%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>22,060,000</t>
+          <t>98,903,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>98,903,000</t>
+          <t>22,060,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>205,760,000</t>
+          <t>64,710,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>64,710,000</t>
+          <t>205,760,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1019,44 +1019,44 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>36,460,000</t>
+          <t>12,008,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>12,008,000</t>
+          <t>36,460,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.63%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1210,46 +1210,46 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>34,100,000</t>
+          <t>36,440,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>36,440,000</t>
+          <t>26,819,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,39 +1261,39 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>15,330,000</t>
+          <t>34,100,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>26,819,000</t>
+          <t>15,330,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1386,24 +1386,24 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,990,000</t>
+          <t>27,850,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,88 +1415,88 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>27,850,000</t>
+          <t>28,906,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>28,906,000</t>
+          <t>7,990,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>材料*-KY</t>
+          <t>長榮鋼</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>41,500,000</t>
+          <t>20,520,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>長榮鋼</t>
+          <t>材料*-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>20,520,000</t>
+          <t>41,500,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
@@ -1791,17 +1791,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>B618BV</t>
+          <t>B618BS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>P09台積3C</t>
+          <t>P09台積2C</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>150,000,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr"/>
@@ -1809,17 +1809,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>B618DK</t>
+          <t>B618BV</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>P12台積3A</t>
+          <t>P09台積3C</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr"/>
@@ -1827,17 +1827,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>B618E6</t>
+          <t>B618DK</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>P14台積5A</t>
+          <t>P12台積3A</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>90,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr"/>
@@ -1845,17 +1845,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>B62942</t>
+          <t>B618E6</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>P11佳世達1</t>
+          <t>P14台積5A</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>27,100,000</t>
+          <t>90,000,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr"/>
@@ -1863,17 +1863,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>B638BG</t>
+          <t>B62942</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>P10聯電2</t>
+          <t>P11佳世達1</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>27,100,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr"/>
@@ -1881,12 +1881,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>B638BJ</t>
+          <t>B638BG</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>P14聯電1A</t>
+          <t>P10聯電2</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>B644C6</t>
+          <t>B638BJ</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>P10鴻海2B</t>
+          <t>P14聯電1A</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr"/>
@@ -1917,17 +1917,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>B644D6</t>
+          <t>B644C6</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>P13鴻海1B</t>
+          <t>P10鴻海2B</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>170,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr"/>
@@ -1935,17 +1935,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>B644DU</t>
+          <t>B644D6</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>P15鴻海1A</t>
+          <t>P13鴻海1B</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>170,000,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr"/>
@@ -1953,17 +1953,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>B644DV</t>
+          <t>B644DU</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>P15鴻海1B</t>
+          <t>P15鴻海1A</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr"/>
@@ -1971,17 +1971,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>B64613</t>
+          <t>B644DV</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>P10國巨2B</t>
+          <t>P15鴻海1B</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>22,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr"/>
@@ -1989,17 +1989,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>B64614</t>
+          <t>B64613</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>P11國巨1</t>
+          <t>P10國巨2B</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>22,000,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr"/>
@@ -2007,12 +2007,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>B67008</t>
+          <t>B64614</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>P15東元1</t>
+          <t>P11國巨1</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -2025,17 +2025,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>B68125</t>
+          <t>B67008</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>P13南科1</t>
+          <t>P15東元1</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>90,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr"/>
@@ -2043,17 +2043,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>B69905</t>
+          <t>B68125</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>P13環球晶2</t>
+          <t>P13南科1</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>90,000,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr"/>
@@ -2061,12 +2061,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>B702AP</t>
+          <t>B69905</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>P09台化1B</t>
+          <t>P13環球晶2</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -2079,12 +2079,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>B702AU</t>
+          <t>B702AP</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>P14台化2A</t>
+          <t>P09台化1B</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>B71310</t>
+          <t>B702AU</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>P10長春1</t>
+          <t>P14台化2A</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>550,000,000</t>
+          <t>100,000,000</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2115,17 +2115,17 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>B718AJ</t>
+          <t>B71310</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>P13中油1A</t>
+          <t>P10長春1</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>30,000,000</t>
+          <t>550,000,000</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2133,17 +2133,17 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>B718AL</t>
+          <t>B718AJ</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>P13中油1C</t>
+          <t>P13中油1A</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>50,000,000</t>
+          <t>30,000,000</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
@@ -2151,17 +2151,17 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>B718AQ</t>
+          <t>B718AL</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>P13中油3A</t>
+          <t>P13中油1C</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>470,000,000</t>
+          <t>50,000,000</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr"/>
@@ -2169,17 +2169,17 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>B718B3</t>
+          <t>B718AQ</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>P13中油7A</t>
+          <t>P13中油3A</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>470,000,000</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr"/>
@@ -2187,17 +2187,17 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>B718BG</t>
+          <t>B718B3</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>P14中油4B</t>
+          <t>P13中油7A</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>200,000,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr"/>
@@ -2205,17 +2205,17 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>B72007</t>
+          <t>B718BG</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>P10長興1</t>
+          <t>P14中油4B</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>465,000,000</t>
+          <t>200,000,000</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr"/>
@@ -2223,17 +2223,17 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>B801AU</t>
+          <t>B72007</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>P14中鋼2</t>
+          <t>P10長興1</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>250,000,000</t>
+          <t>465,000,000</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr"/>
@@ -2241,17 +2241,17 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>B84814</t>
+          <t>B801AU</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>P13亞國1</t>
+          <t>P14中鋼2</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>22,400,000</t>
+          <t>250,000,000</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr"/>
@@ -2259,17 +2259,17 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>B84906</t>
+          <t>B84814</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>P11三發1</t>
+          <t>P13亞國1</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>71,400,000</t>
+          <t>22,400,000</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr"/>
@@ -2277,17 +2277,17 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>B85413</t>
+          <t>B84906</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>P13中龍2</t>
+          <t>P11三發1</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>71,400,000</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr"/>
@@ -2295,17 +2295,17 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>B86211</t>
+          <t>B85413</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>P12富旺1</t>
+          <t>P13中龍2</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>300,113,918</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr"/>
@@ -2313,12 +2313,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>B86412</t>
+          <t>B86211</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>P13興富發1</t>
+          <t>P12富旺1</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>1,000,000,000</t>
+          <t>650,000,000</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>100,000,000</t>
+          <t>300,000,000</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr"/>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>4,390,367,777</t>
+          <t>3,243,214,909</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>2,781,529,186</t>
+          <t>2,674,409,186</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>-2,592,561,059</t>
+          <t>-1,179,135,435</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>773,449,700</t>
+          <t>502,470,927</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr"/>
